--- a/e2e/expectedData/Non_Regular_Gaji_ke-13_yearly.xlsx
+++ b/e2e/expectedData/Non_Regular_Gaji_ke-13_yearly.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="69">
   <si>
     <t>DAFTAR PEMBAYARAN</t>
   </si>
@@ -68,48 +68,51 @@
     <t>IV</t>
   </si>
   <si>
+    <t>Local</t>
+  </si>
+  <si>
+    <t>2026-01</t>
+  </si>
+  <si>
+    <t>850,00</t>
+  </si>
+  <si>
+    <t>200,00</t>
+  </si>
+  <si>
+    <t>0,00</t>
+  </si>
+  <si>
+    <t>1.050,00</t>
+  </si>
+  <si>
+    <t>55,00</t>
+  </si>
+  <si>
+    <t>CELIA MARIA REGO DE FATIMA</t>
+  </si>
+  <si>
+    <t>300,00</t>
+  </si>
+  <si>
+    <t>30,00</t>
+  </si>
+  <si>
+    <t>10,00</t>
+  </si>
+  <si>
+    <t>340,00</t>
+  </si>
+  <si>
+    <t>ADROALDINO DA SILVA NORONHA TOME</t>
+  </si>
+  <si>
+    <t>VI</t>
+  </si>
+  <si>
     <t>Expat</t>
   </si>
   <si>
-    <t>2026-01</t>
-  </si>
-  <si>
-    <t>850,00</t>
-  </si>
-  <si>
-    <t>200,00</t>
-  </si>
-  <si>
-    <t>0,00</t>
-  </si>
-  <si>
-    <t>1.050,00</t>
-  </si>
-  <si>
-    <t>105,00</t>
-  </si>
-  <si>
-    <t>CELIA MARIA REGO DE FATIMA</t>
-  </si>
-  <si>
-    <t>300,00</t>
-  </si>
-  <si>
-    <t>30,00</t>
-  </si>
-  <si>
-    <t>10,00</t>
-  </si>
-  <si>
-    <t>340,00</t>
-  </si>
-  <si>
-    <t>ADROALDINO DA SILVA NORONHA TOME</t>
-  </si>
-  <si>
-    <t>VI</t>
-  </si>
-  <si>
     <t>120,00</t>
   </si>
   <si>
@@ -179,6 +182,9 @@
     <t>CLAUDIO DA COSTA ALVES</t>
   </si>
   <si>
+    <t>Outsource</t>
+  </si>
+  <si>
     <t>210,00</t>
   </si>
   <si>
@@ -188,10 +194,10 @@
     <t>4.864,00</t>
   </si>
   <si>
-    <t>297,00</t>
-  </si>
-  <si>
-    <t>DILI, 26 August 2026</t>
+    <t>247,00</t>
+  </si>
+  <si>
+    <t>DILI, 09 September 2026</t>
   </si>
   <si>
     <t>PREPARED BY</t>
@@ -787,13 +793,13 @@
         <v>30</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>18</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>27</v>
@@ -805,10 +811,10 @@
         <v>21</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L8" s="3" t="s">
         <v>21</v>
@@ -819,13 +825,13 @@
         <v>79001</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>18</v>
@@ -834,10 +840,10 @@
         <v>20</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I9" s="3" t="s">
         <v>21</v>
@@ -857,25 +863,25 @@
         <v>91009</v>
       </c>
       <c r="B10" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C10" s="3" t="s">
-        <v>35</v>
-      </c>
       <c r="D10" s="3" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>18</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I10" s="3" t="s">
         <v>21</v>
@@ -884,10 +890,10 @@
         <v>21</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -895,37 +901,37 @@
         <v>74003</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>18</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>21</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J11" s="3" t="s">
         <v>21</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -933,13 +939,13 @@
         <v>91015</v>
       </c>
       <c r="B12" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D12" s="3" t="s">
         <v>44</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>43</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>18</v>
@@ -948,13 +954,13 @@
         <v>20</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>21</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>26</v>
@@ -971,19 +977,19 @@
         <v>26013</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>30</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>18</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>27</v>
@@ -995,10 +1001,10 @@
         <v>21</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="L13" s="3" t="s">
         <v>21</v>
@@ -1009,19 +1015,19 @@
         <v>95008</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>16</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>18</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>27</v>
@@ -1036,10 +1042,10 @@
         <v>21</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -1047,22 +1053,22 @@
         <v>24005</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>30</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>17</v>
+        <v>55</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>18</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>21</v>
@@ -1074,7 +1080,7 @@
         <v>27</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="L15" s="3" t="s">
         <v>21</v>
@@ -1082,7 +1088,7 @@
     </row>
     <row r="16" spans="1:12">
       <c r="A16" s="4" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
@@ -1094,10 +1100,10 @@
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
       <c r="K16" s="4" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="L16" s="4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="17" spans="1:12">
@@ -1105,13 +1111,13 @@
     </row>
     <row r="18" spans="1:12">
       <c r="A18" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G18"/>
     </row>
     <row r="19" spans="1:12">
       <c r="A19" s="5" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B19" s="5"/>
       <c r="C19" s="5"/>
@@ -1119,7 +1125,7 @@
       <c r="E19" s="5"/>
       <c r="F19" s="5"/>
       <c r="G19" s="5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="H19" s="5"/>
       <c r="I19" s="5"/>
@@ -1129,11 +1135,11 @@
     </row>
     <row r="20" spans="1:12">
       <c r="A20" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E20"/>
       <c r="I20" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="21" spans="1:12" customHeight="1" ht="37.5">
@@ -1143,20 +1149,20 @@
     </row>
     <row r="22" spans="1:12">
       <c r="A22" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E22"/>
       <c r="I22" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="23" spans="1:12">
       <c r="A23" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E23"/>
       <c r="I23" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
   </sheetData>

--- a/e2e/expectedData/Non_Regular_Gaji_ke-13_yearly.xlsx
+++ b/e2e/expectedData/Non_Regular_Gaji_ke-13_yearly.xlsx
@@ -110,24 +110,27 @@
     <t>VI</t>
   </si>
   <si>
+    <t>Outsource</t>
+  </si>
+  <si>
+    <t>120,00</t>
+  </si>
+  <si>
+    <t>50,00</t>
+  </si>
+  <si>
+    <t>180,00</t>
+  </si>
+  <si>
+    <t>DIAN EVIYANTI APLUGI</t>
+  </si>
+  <si>
+    <t>III</t>
+  </si>
+  <si>
     <t>Expat</t>
   </si>
   <si>
-    <t>120,00</t>
-  </si>
-  <si>
-    <t>50,00</t>
-  </si>
-  <si>
-    <t>180,00</t>
-  </si>
-  <si>
-    <t>DIAN EVIYANTI APLUGI</t>
-  </si>
-  <si>
-    <t>III</t>
-  </si>
-  <si>
     <t>FRIESCA AMELIA</t>
   </si>
   <si>
@@ -182,9 +185,6 @@
     <t>CLAUDIO DA COSTA ALVES</t>
   </si>
   <si>
-    <t>Outsource</t>
-  </si>
-  <si>
     <t>210,00</t>
   </si>
   <si>
@@ -197,7 +197,7 @@
     <t>247,00</t>
   </si>
   <si>
-    <t>DILI, 09 September 2026</t>
+    <t>DILI, 10 September 2026</t>
   </si>
   <si>
     <t>PREPARED BY</t>
@@ -831,7 +831,7 @@
         <v>36</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>18</v>
@@ -863,22 +863,22 @@
         <v>91009</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>36</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>18</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>33</v>
@@ -890,10 +890,10 @@
         <v>21</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -901,22 +901,22 @@
         <v>74003</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>18</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>21</v>
@@ -928,10 +928,10 @@
         <v>21</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -939,13 +939,13 @@
         <v>91015</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>36</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>18</v>
@@ -960,7 +960,7 @@
         <v>21</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>26</v>
@@ -977,19 +977,19 @@
         <v>26013</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>30</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>18</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>27</v>
@@ -1004,7 +1004,7 @@
         <v>33</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L13" s="3" t="s">
         <v>21</v>
@@ -1015,19 +1015,19 @@
         <v>95008</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>16</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>18</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>27</v>
@@ -1042,10 +1042,10 @@
         <v>21</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -1053,19 +1053,19 @@
         <v>24005</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>30</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>55</v>
+        <v>31</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>18</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>33</v>
